--- a/Report/ReportApplyLeave.xlsx
+++ b/Report/ReportApplyLeave.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ppham\Documents\Do an\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F62621D-33EF-4353-9D6C-2D53A3B6DFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0CEC98-C2CA-404E-B794-A2EAED05DC0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -548,16 +548,17 @@
   <dimension ref="B2:L14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.109375" customWidth="1"/>
-    <col min="3" max="3" width="14.21875" customWidth="1"/>
-    <col min="4" max="4" width="12.77734375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" style="5" customWidth="1"/>
-    <col min="6" max="6" width="15" style="5" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="11.77734375" style="5" customWidth="1"/>
     <col min="7" max="7" width="17.21875" customWidth="1"/>
-    <col min="8" max="8" width="16.33203125" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" customWidth="1"/>
     <col min="9" max="9" width="50.88671875" customWidth="1"/>
-    <col min="10" max="10" width="13.21875" customWidth="1"/>
-    <col min="11" max="11" width="38.44140625" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="37.6640625" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
